--- a/tests/test_input/test_metadata.xlsx
+++ b/tests/test_input/test_metadata.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,11 +559,6 @@
           <t>SeMPyRO_annotations_IRI</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SeMPyRO_add_rdf_model</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,11 +589,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>http://example.com/TestClass</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/tests/test_input/test_metadata.xlsx
+++ b/tests/test_input/test_metadata.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Controlled vocabluary (if applicable)</t>
+          <t>Controlled vocabulary (if applicable)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
